--- a/data/final/series/yahoo_nasdaq.xlsx
+++ b/data/final/series/yahoo_nasdaq.xlsx
@@ -917,7 +917,7 @@
         <v>46295</v>
       </c>
       <c r="B62" t="n">
-        <v>26506.990234</v>
+        <v>26390.132812</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_nasdaq.xlsx
+++ b/data/final/series/yahoo_nasdaq.xlsx
@@ -917,7 +917,7 @@
         <v>46295</v>
       </c>
       <c r="B62" t="n">
-        <v>26390.132812</v>
+        <v>26360.449219</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_nasdaq.xlsx
+++ b/data/final/series/yahoo_nasdaq.xlsx
@@ -917,7 +917,7 @@
         <v>46295</v>
       </c>
       <c r="B62" t="n">
-        <v>26360.449219</v>
+        <v>26037.785156</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_nasdaq.xlsx
+++ b/data/final/series/yahoo_nasdaq.xlsx
@@ -917,7 +917,7 @@
         <v>46295</v>
       </c>
       <c r="B62" t="n">
-        <v>26037.785156</v>
+        <v>26405.673828</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_nasdaq.xlsx
+++ b/data/final/series/yahoo_nasdaq.xlsx
@@ -917,7 +917,7 @@
         <v>46295</v>
       </c>
       <c r="B62" t="n">
-        <v>26405.673828</v>
+        <v>26356.910156</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_nasdaq.xlsx
+++ b/data/final/series/yahoo_nasdaq.xlsx
@@ -917,7 +917,7 @@
         <v>46295</v>
       </c>
       <c r="B62" t="n">
-        <v>26356.910156</v>
+        <v>26333.039062</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_nasdaq.xlsx
+++ b/data/final/series/yahoo_nasdaq.xlsx
@@ -917,7 +917,7 @@
         <v>46295</v>
       </c>
       <c r="B62" t="n">
-        <v>26333.039062</v>
+        <v>26209.451172</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_nasdaq.xlsx
+++ b/data/final/series/yahoo_nasdaq.xlsx
@@ -917,7 +917,7 @@
         <v>46295</v>
       </c>
       <c r="B62" t="n">
-        <v>26209.451172</v>
+        <v>26026.601562</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_nasdaq.xlsx
+++ b/data/final/series/yahoo_nasdaq.xlsx
@@ -917,7 +917,7 @@
         <v>46295</v>
       </c>
       <c r="B62" t="n">
-        <v>26026.601562</v>
+        <v>26133.207031</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_nasdaq.xlsx
+++ b/data/final/series/yahoo_nasdaq.xlsx
@@ -917,7 +917,7 @@
         <v>46295</v>
       </c>
       <c r="B62" t="n">
-        <v>26133.207031</v>
+        <v>26407.919922</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_nasdaq.xlsx
+++ b/data/final/series/yahoo_nasdaq.xlsx
@@ -917,7 +917,7 @@
         <v>46295</v>
       </c>
       <c r="B62" t="n">
-        <v>26407.919922</v>
+        <v>26423.677734</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_nasdaq.xlsx
+++ b/data/final/series/yahoo_nasdaq.xlsx
@@ -917,7 +917,7 @@
         <v>46295</v>
       </c>
       <c r="B62" t="n">
-        <v>26423.677734</v>
+        <v>26522.539062</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_nasdaq.xlsx
+++ b/data/final/series/yahoo_nasdaq.xlsx
@@ -917,7 +917,7 @@
         <v>46295</v>
       </c>
       <c r="B62" t="n">
-        <v>26522.539062</v>
+        <v>27005.107422</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_nasdaq.xlsx
+++ b/data/final/series/yahoo_nasdaq.xlsx
@@ -917,7 +917,7 @@
         <v>46295</v>
       </c>
       <c r="B62" t="n">
-        <v>27005.107422</v>
+        <v>27251.701172</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_nasdaq.xlsx
+++ b/data/final/series/yahoo_nasdaq.xlsx
@@ -917,7 +917,7 @@
         <v>46295</v>
       </c>
       <c r="B62" t="n">
-        <v>27251.701172</v>
+        <v>27249.957031</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_nasdaq.xlsx
+++ b/data/final/series/yahoo_nasdaq.xlsx
@@ -917,7 +917,7 @@
         <v>46295</v>
       </c>
       <c r="B62" t="n">
-        <v>27249.957031</v>
+        <v>26969.003906</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_nasdaq.xlsx
+++ b/data/final/series/yahoo_nasdaq.xlsx
@@ -917,7 +917,7 @@
         <v>46295</v>
       </c>
       <c r="B62" t="n">
-        <v>26969.003906</v>
+        <v>26805.265625</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_nasdaq.xlsx
+++ b/data/final/series/yahoo_nasdaq.xlsx
@@ -917,7 +917,7 @@
         <v>46295</v>
       </c>
       <c r="B62" t="n">
-        <v>26805.265625</v>
+        <v>26794.8125</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_nasdaq.xlsx
+++ b/data/final/series/yahoo_nasdaq.xlsx
@@ -917,7 +917,7 @@
         <v>46295</v>
       </c>
       <c r="B62" t="n">
-        <v>26794.8125</v>
+        <v>26965.560547</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_nasdaq.xlsx
+++ b/data/final/series/yahoo_nasdaq.xlsx
@@ -917,7 +917,7 @@
         <v>46295</v>
       </c>
       <c r="B62" t="n">
-        <v>26965.560547</v>
+        <v>27068.720703</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_nasdaq.xlsx
+++ b/data/final/series/yahoo_nasdaq.xlsx
@@ -917,7 +917,7 @@
         <v>46295</v>
       </c>
       <c r="B62" t="n">
-        <v>27068.720703</v>
+        <v>26903.330078</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_nasdaq.xlsx
+++ b/data/final/series/yahoo_nasdaq.xlsx
@@ -917,7 +917,7 @@
         <v>46295</v>
       </c>
       <c r="B62" t="n">
-        <v>26903.330078</v>
+        <v>26899.5</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_nasdaq.xlsx
+++ b/data/final/series/yahoo_nasdaq.xlsx
@@ -917,7 +917,7 @@
         <v>46295</v>
       </c>
       <c r="B62" t="n">
-        <v>26899.5</v>
+        <v>26774.152344</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_nasdaq.xlsx
+++ b/data/final/series/yahoo_nasdaq.xlsx
@@ -917,7 +917,7 @@
         <v>46295</v>
       </c>
       <c r="B62" t="n">
-        <v>26774.152344</v>
+        <v>26779.210938</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_nasdaq.xlsx
+++ b/data/final/series/yahoo_nasdaq.xlsx
@@ -917,7 +917,7 @@
         <v>46295</v>
       </c>
       <c r="B62" t="n">
-        <v>26779.210938</v>
+        <v>27077.017578</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_nasdaq.xlsx
+++ b/data/final/series/yahoo_nasdaq.xlsx
@@ -917,7 +917,7 @@
         <v>46295</v>
       </c>
       <c r="B62" t="n">
-        <v>27077.017578</v>
+        <v>27062.792969</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_nasdaq.xlsx
+++ b/data/final/series/yahoo_nasdaq.xlsx
@@ -434,490 +434,490 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="B2" t="n">
-        <v>14448.580078</v>
+        <v>15498.389648</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>44500</v>
+        <v>44530</v>
       </c>
       <c r="B3" t="n">
-        <v>15498.389648</v>
+        <v>15537.69043</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44530</v>
+        <v>44561</v>
       </c>
       <c r="B4" t="n">
-        <v>15537.69043</v>
+        <v>15644.969727</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>44592</v>
       </c>
       <c r="B5" t="n">
-        <v>15644.969727</v>
+        <v>14239.879883</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>44592</v>
+        <v>44620</v>
       </c>
       <c r="B6" t="n">
-        <v>14239.879883</v>
+        <v>13751.400391</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>44620</v>
+        <v>44651</v>
       </c>
       <c r="B7" t="n">
-        <v>13751.400391</v>
+        <v>14220.519531</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>44651</v>
+        <v>44681</v>
       </c>
       <c r="B8" t="n">
-        <v>14220.519531</v>
+        <v>12334.639648</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>44681</v>
+        <v>44712</v>
       </c>
       <c r="B9" t="n">
-        <v>12334.639648</v>
+        <v>12081.389648</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>44712</v>
+        <v>44742</v>
       </c>
       <c r="B10" t="n">
-        <v>12081.389648</v>
+        <v>11028.740234</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>44742</v>
+        <v>44773</v>
       </c>
       <c r="B11" t="n">
-        <v>11028.740234</v>
+        <v>12390.69043</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>44773</v>
+        <v>44804</v>
       </c>
       <c r="B12" t="n">
-        <v>12390.69043</v>
+        <v>11816.200195</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>44804</v>
+        <v>44834</v>
       </c>
       <c r="B13" t="n">
-        <v>11816.200195</v>
+        <v>10575.620117</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>44834</v>
+        <v>44865</v>
       </c>
       <c r="B14" t="n">
-        <v>10575.620117</v>
+        <v>10988.150391</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>44865</v>
+        <v>44895</v>
       </c>
       <c r="B15" t="n">
-        <v>10988.150391</v>
+        <v>11468</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>44895</v>
+        <v>44926</v>
       </c>
       <c r="B16" t="n">
-        <v>11468</v>
+        <v>10466.480469</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>44926</v>
+        <v>44957</v>
       </c>
       <c r="B17" t="n">
-        <v>10466.480469</v>
+        <v>11584.549805</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>44957</v>
+        <v>44985</v>
       </c>
       <c r="B18" t="n">
-        <v>11584.549805</v>
+        <v>11455.540039</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>44985</v>
+        <v>45016</v>
       </c>
       <c r="B19" t="n">
-        <v>11455.540039</v>
+        <v>12221.910156</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45016</v>
+        <v>45046</v>
       </c>
       <c r="B20" t="n">
-        <v>12221.910156</v>
+        <v>12226.580078</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45046</v>
+        <v>45077</v>
       </c>
       <c r="B21" t="n">
-        <v>12226.580078</v>
+        <v>12935.290039</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45077</v>
+        <v>45107</v>
       </c>
       <c r="B22" t="n">
-        <v>12935.290039</v>
+        <v>13787.919922</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45107</v>
+        <v>45138</v>
       </c>
       <c r="B23" t="n">
-        <v>13787.919922</v>
+        <v>14346.019531</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45138</v>
+        <v>45169</v>
       </c>
       <c r="B24" t="n">
-        <v>14346.019531</v>
+        <v>14034.969727</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45169</v>
+        <v>45199</v>
       </c>
       <c r="B25" t="n">
-        <v>14034.969727</v>
+        <v>13219.320312</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45199</v>
+        <v>45230</v>
       </c>
       <c r="B26" t="n">
-        <v>13219.320312</v>
+        <v>12851.240234</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45230</v>
+        <v>45260</v>
       </c>
       <c r="B27" t="n">
-        <v>12851.240234</v>
+        <v>14226.219727</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45260</v>
+        <v>45291</v>
       </c>
       <c r="B28" t="n">
-        <v>14226.219727</v>
+        <v>15011.349609</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45291</v>
+        <v>45322</v>
       </c>
       <c r="B29" t="n">
-        <v>15011.349609</v>
+        <v>15164.009766</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45322</v>
+        <v>45351</v>
       </c>
       <c r="B30" t="n">
-        <v>15164.009766</v>
+        <v>16091.919922</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45351</v>
+        <v>45382</v>
       </c>
       <c r="B31" t="n">
-        <v>16091.919922</v>
+        <v>16379.459961</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45382</v>
+        <v>45412</v>
       </c>
       <c r="B32" t="n">
-        <v>16379.459961</v>
+        <v>15657.820312</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45412</v>
+        <v>45443</v>
       </c>
       <c r="B33" t="n">
-        <v>15657.820312</v>
+        <v>16735.019531</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45443</v>
+        <v>45473</v>
       </c>
       <c r="B34" t="n">
-        <v>16735.019531</v>
+        <v>17732.599609</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45473</v>
+        <v>45504</v>
       </c>
       <c r="B35" t="n">
-        <v>17732.599609</v>
+        <v>17599.400391</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45504</v>
+        <v>45535</v>
       </c>
       <c r="B36" t="n">
-        <v>17599.400391</v>
+        <v>17713.619141</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45535</v>
+        <v>45565</v>
       </c>
       <c r="B37" t="n">
-        <v>17713.619141</v>
+        <v>18189.169922</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45565</v>
+        <v>45596</v>
       </c>
       <c r="B38" t="n">
-        <v>18189.169922</v>
+        <v>18095.150391</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45596</v>
+        <v>45626</v>
       </c>
       <c r="B39" t="n">
-        <v>18095.150391</v>
+        <v>19218.169922</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45626</v>
+        <v>45657</v>
       </c>
       <c r="B40" t="n">
-        <v>19218.169922</v>
+        <v>19310.789062</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45657</v>
+        <v>45688</v>
       </c>
       <c r="B41" t="n">
-        <v>19310.789062</v>
+        <v>19627.439453</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45688</v>
+        <v>45716</v>
       </c>
       <c r="B42" t="n">
-        <v>19627.439453</v>
+        <v>18847.279297</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45716</v>
+        <v>45747</v>
       </c>
       <c r="B43" t="n">
-        <v>18847.279297</v>
+        <v>17299.289062</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45747</v>
+        <v>45777</v>
       </c>
       <c r="B44" t="n">
-        <v>17299.289062</v>
+        <v>17446.339844</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45777</v>
+        <v>45808</v>
       </c>
       <c r="B45" t="n">
-        <v>17446.339844</v>
+        <v>19113.769531</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45808</v>
+        <v>45838</v>
       </c>
       <c r="B46" t="n">
-        <v>19113.769531</v>
+        <v>20369.730469</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45838</v>
+        <v>45869</v>
       </c>
       <c r="B47" t="n">
-        <v>20369.730469</v>
+        <v>21122.449219</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45869</v>
+        <v>45900</v>
       </c>
       <c r="B48" t="n">
-        <v>21122.449219</v>
+        <v>21455.550781</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45900</v>
+        <v>45930</v>
       </c>
       <c r="B49" t="n">
-        <v>21455.550781</v>
+        <v>22660.009766</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>45930</v>
+        <v>45961</v>
       </c>
       <c r="B50" t="n">
-        <v>22660.009766</v>
+        <v>23724.960938</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>45961</v>
+        <v>45991</v>
       </c>
       <c r="B51" t="n">
-        <v>23724.960938</v>
+        <v>23365.689453</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>45991</v>
+        <v>46022</v>
       </c>
       <c r="B52" t="n">
-        <v>23365.689453</v>
+        <v>23241.990234</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>46022</v>
+        <v>46053</v>
       </c>
       <c r="B53" t="n">
-        <v>23241.990234</v>
+        <v>23461.820312</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B54" t="n">
-        <v>23461.820312</v>
+        <v>22668.210938</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>46081</v>
+        <v>46112</v>
       </c>
       <c r="B55" t="n">
-        <v>22668.210938</v>
+        <v>21590.630859</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>46112</v>
+        <v>46142</v>
       </c>
       <c r="B56" t="n">
-        <v>21590.630859</v>
+        <v>24892.310547</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>46142</v>
+        <v>46173</v>
       </c>
       <c r="B57" t="n">
-        <v>24892.310547</v>
+        <v>26972.619141</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="B58" t="n">
-        <v>26972.619141</v>
+        <v>26213.720703</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="B59" t="n">
-        <v>26213.720703</v>
+        <v>25373.849609</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="B60" t="n">
-        <v>25373.849609</v>
+        <v>26370.890625</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="B61" t="n">
-        <v>26370.890625</v>
+        <v>26861.060547</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="B62" t="n">
-        <v>27062.792969</v>
+        <v>26818.607422</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_nasdaq.xlsx
+++ b/data/final/series/yahoo_nasdaq.xlsx
@@ -917,7 +917,7 @@
         <v>46326</v>
       </c>
       <c r="B62" t="n">
-        <v>26818.607422</v>
+        <v>27210.888672</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_nasdaq.xlsx
+++ b/data/final/series/yahoo_nasdaq.xlsx
@@ -917,7 +917,7 @@
         <v>46326</v>
       </c>
       <c r="B62" t="n">
-        <v>27210.888672</v>
+        <v>27222.126953</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_nasdaq.xlsx
+++ b/data/final/series/yahoo_nasdaq.xlsx
@@ -917,7 +917,7 @@
         <v>46326</v>
       </c>
       <c r="B62" t="n">
-        <v>27222.126953</v>
+        <v>27190.859375</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_nasdaq.xlsx
+++ b/data/final/series/yahoo_nasdaq.xlsx
@@ -917,7 +917,7 @@
         <v>46326</v>
       </c>
       <c r="B62" t="n">
-        <v>27190.859375</v>
+        <v>27504.978516</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_nasdaq.xlsx
+++ b/data/final/series/yahoo_nasdaq.xlsx
@@ -917,7 +917,7 @@
         <v>46326</v>
       </c>
       <c r="B62" t="n">
-        <v>27504.978516</v>
+        <v>27662.966797</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_nasdaq.xlsx
+++ b/data/final/series/yahoo_nasdaq.xlsx
@@ -917,7 +917,7 @@
         <v>46326</v>
       </c>
       <c r="B62" t="n">
-        <v>27662.966797</v>
+        <v>27498.011719</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_nasdaq.xlsx
+++ b/data/final/series/yahoo_nasdaq.xlsx
@@ -917,7 +917,7 @@
         <v>46326</v>
       </c>
       <c r="B62" t="n">
-        <v>27498.011719</v>
+        <v>27173.046875</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_nasdaq.xlsx
+++ b/data/final/series/yahoo_nasdaq.xlsx
@@ -917,7 +917,7 @@
         <v>46326</v>
       </c>
       <c r="B62" t="n">
-        <v>27173.046875</v>
+        <v>27225.183594</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_nasdaq.xlsx
+++ b/data/final/series/yahoo_nasdaq.xlsx
@@ -917,7 +917,7 @@
         <v>46326</v>
       </c>
       <c r="B62" t="n">
-        <v>27225.183594</v>
+        <v>27350.091797</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_nasdaq.xlsx
+++ b/data/final/series/yahoo_nasdaq.xlsx
@@ -917,7 +917,7 @@
         <v>46326</v>
       </c>
       <c r="B62" t="n">
-        <v>27350.091797</v>
+        <v>27376.107422</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_nasdaq.xlsx
+++ b/data/final/series/yahoo_nasdaq.xlsx
@@ -917,7 +917,7 @@
         <v>46326</v>
       </c>
       <c r="B62" t="n">
-        <v>27376.107422</v>
+        <v>27366.169922</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_nasdaq.xlsx
+++ b/data/final/series/yahoo_nasdaq.xlsx
@@ -917,7 +917,7 @@
         <v>46326</v>
       </c>
       <c r="B62" t="n">
-        <v>27366.169922</v>
+        <v>27238.013672</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_nasdaq.xlsx
+++ b/data/final/series/yahoo_nasdaq.xlsx
@@ -917,7 +917,7 @@
         <v>46326</v>
       </c>
       <c r="B62" t="n">
-        <v>27238.013672</v>
+        <v>27254.84375</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_nasdaq.xlsx
+++ b/data/final/series/yahoo_nasdaq.xlsx
@@ -917,7 +917,7 @@
         <v>46326</v>
       </c>
       <c r="B62" t="n">
-        <v>27254.84375</v>
+        <v>27187.478516</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_nasdaq.xlsx
+++ b/data/final/series/yahoo_nasdaq.xlsx
@@ -917,7 +917,7 @@
         <v>46326</v>
       </c>
       <c r="B62" t="n">
-        <v>27187.478516</v>
+        <v>26954.634766</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_nasdaq.xlsx
+++ b/data/final/series/yahoo_nasdaq.xlsx
@@ -917,7 +917,7 @@
         <v>46326</v>
       </c>
       <c r="B62" t="n">
-        <v>26954.634766</v>
+        <v>26941.662109</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_nasdaq.xlsx
+++ b/data/final/series/yahoo_nasdaq.xlsx
@@ -917,7 +917,7 @@
         <v>46326</v>
       </c>
       <c r="B62" t="n">
-        <v>26941.662109</v>
+        <v>26452.943359</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_nasdaq.xlsx
+++ b/data/final/series/yahoo_nasdaq.xlsx
@@ -917,7 +917,7 @@
         <v>46326</v>
       </c>
       <c r="B62" t="n">
-        <v>26452.943359</v>
+        <v>26499.583984</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_nasdaq.xlsx
+++ b/data/final/series/yahoo_nasdaq.xlsx
@@ -917,7 +917,7 @@
         <v>46326</v>
       </c>
       <c r="B62" t="n">
-        <v>26499.583984</v>
+        <v>26140.029297</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_nasdaq.xlsx
+++ b/data/final/series/yahoo_nasdaq.xlsx
@@ -917,7 +917,7 @@
         <v>46326</v>
       </c>
       <c r="B62" t="n">
-        <v>26140.029297</v>
+        <v>26522.501953</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_nasdaq.xlsx
+++ b/data/final/series/yahoo_nasdaq.xlsx
@@ -917,7 +917,7 @@
         <v>46326</v>
       </c>
       <c r="B62" t="n">
-        <v>26522.501953</v>
+        <v>26544.773438</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_nasdaq.xlsx
+++ b/data/final/series/yahoo_nasdaq.xlsx
@@ -917,7 +917,7 @@
         <v>46326</v>
       </c>
       <c r="B62" t="n">
-        <v>26544.773438</v>
+        <v>26607.212891</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_nasdaq.xlsx
+++ b/data/final/series/yahoo_nasdaq.xlsx
@@ -917,7 +917,7 @@
         <v>46326</v>
       </c>
       <c r="B62" t="n">
-        <v>26607.212891</v>
+        <v>26096.677734</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_nasdaq.xlsx
+++ b/data/final/series/yahoo_nasdaq.xlsx
@@ -917,7 +917,7 @@
         <v>46326</v>
       </c>
       <c r="B62" t="n">
-        <v>26096.677734</v>
+        <v>25972.888672</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_nasdaq.xlsx
+++ b/data/final/series/yahoo_nasdaq.xlsx
@@ -917,7 +917,7 @@
         <v>46326</v>
       </c>
       <c r="B62" t="n">
-        <v>25972.888672</v>
+        <v>25955.339844</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_nasdaq.xlsx
+++ b/data/final/series/yahoo_nasdaq.xlsx
@@ -917,7 +917,7 @@
         <v>46326</v>
       </c>
       <c r="B62" t="n">
-        <v>25955.339844</v>
+        <v>26216.0625</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_nasdaq.xlsx
+++ b/data/final/series/yahoo_nasdaq.xlsx
@@ -917,7 +917,7 @@
         <v>46326</v>
       </c>
       <c r="B62" t="n">
-        <v>26216.0625</v>
+        <v>26448.109375</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_nasdaq.xlsx
+++ b/data/final/series/yahoo_nasdaq.xlsx
@@ -917,7 +917,7 @@
         <v>46326</v>
       </c>
       <c r="B62" t="n">
-        <v>26448.109375</v>
+        <v>26453.009766</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_nasdaq.xlsx
+++ b/data/final/series/yahoo_nasdaq.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B62"/>
+  <dimension ref="A1:B61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -434,490 +434,482 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>44500</v>
+        <v>44530</v>
       </c>
       <c r="B2" t="n">
-        <v>15498.389648</v>
+        <v>15537.69043</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>44530</v>
+        <v>44561</v>
       </c>
       <c r="B3" t="n">
-        <v>15537.69043</v>
+        <v>15644.969727</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44561</v>
+        <v>44592</v>
       </c>
       <c r="B4" t="n">
-        <v>15644.969727</v>
+        <v>14239.879883</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44592</v>
+        <v>44620</v>
       </c>
       <c r="B5" t="n">
-        <v>14239.879883</v>
+        <v>13751.400391</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>44620</v>
+        <v>44651</v>
       </c>
       <c r="B6" t="n">
-        <v>13751.400391</v>
+        <v>14220.519531</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>44651</v>
+        <v>44681</v>
       </c>
       <c r="B7" t="n">
-        <v>14220.519531</v>
+        <v>12334.639648</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>44681</v>
+        <v>44712</v>
       </c>
       <c r="B8" t="n">
-        <v>12334.639648</v>
+        <v>12081.389648</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>44712</v>
+        <v>44742</v>
       </c>
       <c r="B9" t="n">
-        <v>12081.389648</v>
+        <v>11028.740234</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>44742</v>
+        <v>44773</v>
       </c>
       <c r="B10" t="n">
-        <v>11028.740234</v>
+        <v>12390.69043</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>44773</v>
+        <v>44804</v>
       </c>
       <c r="B11" t="n">
-        <v>12390.69043</v>
+        <v>11816.200195</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>44804</v>
+        <v>44834</v>
       </c>
       <c r="B12" t="n">
-        <v>11816.200195</v>
+        <v>10575.620117</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>44834</v>
+        <v>44865</v>
       </c>
       <c r="B13" t="n">
-        <v>10575.620117</v>
+        <v>10988.150391</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>44865</v>
+        <v>44895</v>
       </c>
       <c r="B14" t="n">
-        <v>10988.150391</v>
+        <v>11468</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>44895</v>
+        <v>44926</v>
       </c>
       <c r="B15" t="n">
-        <v>11468</v>
+        <v>10466.480469</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>44926</v>
+        <v>44957</v>
       </c>
       <c r="B16" t="n">
-        <v>10466.480469</v>
+        <v>11584.549805</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>44957</v>
+        <v>44985</v>
       </c>
       <c r="B17" t="n">
-        <v>11584.549805</v>
+        <v>11455.540039</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>44985</v>
+        <v>45016</v>
       </c>
       <c r="B18" t="n">
-        <v>11455.540039</v>
+        <v>12221.910156</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45016</v>
+        <v>45046</v>
       </c>
       <c r="B19" t="n">
-        <v>12221.910156</v>
+        <v>12226.580078</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45046</v>
+        <v>45077</v>
       </c>
       <c r="B20" t="n">
-        <v>12226.580078</v>
+        <v>12935.290039</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45077</v>
+        <v>45107</v>
       </c>
       <c r="B21" t="n">
-        <v>12935.290039</v>
+        <v>13787.919922</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45107</v>
+        <v>45138</v>
       </c>
       <c r="B22" t="n">
-        <v>13787.919922</v>
+        <v>14346.019531</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45138</v>
+        <v>45169</v>
       </c>
       <c r="B23" t="n">
-        <v>14346.019531</v>
+        <v>14034.969727</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45169</v>
+        <v>45199</v>
       </c>
       <c r="B24" t="n">
-        <v>14034.969727</v>
+        <v>13219.320312</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45199</v>
+        <v>45230</v>
       </c>
       <c r="B25" t="n">
-        <v>13219.320312</v>
+        <v>12851.240234</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45230</v>
+        <v>45260</v>
       </c>
       <c r="B26" t="n">
-        <v>12851.240234</v>
+        <v>14226.219727</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45260</v>
+        <v>45291</v>
       </c>
       <c r="B27" t="n">
-        <v>14226.219727</v>
+        <v>15011.349609</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45291</v>
+        <v>45322</v>
       </c>
       <c r="B28" t="n">
-        <v>15011.349609</v>
+        <v>15164.009766</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45322</v>
+        <v>45351</v>
       </c>
       <c r="B29" t="n">
-        <v>15164.009766</v>
+        <v>16091.919922</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45351</v>
+        <v>45382</v>
       </c>
       <c r="B30" t="n">
-        <v>16091.919922</v>
+        <v>16379.459961</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45382</v>
+        <v>45412</v>
       </c>
       <c r="B31" t="n">
-        <v>16379.459961</v>
+        <v>15657.820312</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45412</v>
+        <v>45443</v>
       </c>
       <c r="B32" t="n">
-        <v>15657.820312</v>
+        <v>16735.019531</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45443</v>
+        <v>45473</v>
       </c>
       <c r="B33" t="n">
-        <v>16735.019531</v>
+        <v>17732.599609</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45473</v>
+        <v>45504</v>
       </c>
       <c r="B34" t="n">
-        <v>17732.599609</v>
+        <v>17599.400391</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45504</v>
+        <v>45535</v>
       </c>
       <c r="B35" t="n">
-        <v>17599.400391</v>
+        <v>17713.619141</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45535</v>
+        <v>45565</v>
       </c>
       <c r="B36" t="n">
-        <v>17713.619141</v>
+        <v>18189.169922</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45565</v>
+        <v>45596</v>
       </c>
       <c r="B37" t="n">
-        <v>18189.169922</v>
+        <v>18095.150391</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45596</v>
+        <v>45626</v>
       </c>
       <c r="B38" t="n">
-        <v>18095.150391</v>
+        <v>19218.169922</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45626</v>
+        <v>45657</v>
       </c>
       <c r="B39" t="n">
-        <v>19218.169922</v>
+        <v>19310.789062</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45657</v>
+        <v>45688</v>
       </c>
       <c r="B40" t="n">
-        <v>19310.789062</v>
+        <v>19627.439453</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45688</v>
+        <v>45716</v>
       </c>
       <c r="B41" t="n">
-        <v>19627.439453</v>
+        <v>18847.279297</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45716</v>
+        <v>45747</v>
       </c>
       <c r="B42" t="n">
-        <v>18847.279297</v>
+        <v>17299.289062</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45747</v>
+        <v>45777</v>
       </c>
       <c r="B43" t="n">
-        <v>17299.289062</v>
+        <v>17446.339844</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45777</v>
+        <v>45808</v>
       </c>
       <c r="B44" t="n">
-        <v>17446.339844</v>
+        <v>19113.769531</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45808</v>
+        <v>45838</v>
       </c>
       <c r="B45" t="n">
-        <v>19113.769531</v>
+        <v>20369.730469</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45838</v>
+        <v>45869</v>
       </c>
       <c r="B46" t="n">
-        <v>20369.730469</v>
+        <v>21122.449219</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45869</v>
+        <v>45900</v>
       </c>
       <c r="B47" t="n">
-        <v>21122.449219</v>
+        <v>21455.550781</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45900</v>
+        <v>45930</v>
       </c>
       <c r="B48" t="n">
-        <v>21455.550781</v>
+        <v>22660.009766</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45930</v>
+        <v>45961</v>
       </c>
       <c r="B49" t="n">
-        <v>22660.009766</v>
+        <v>23724.960938</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>45961</v>
+        <v>45991</v>
       </c>
       <c r="B50" t="n">
-        <v>23724.960938</v>
+        <v>23365.689453</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>45991</v>
+        <v>46022</v>
       </c>
       <c r="B51" t="n">
-        <v>23365.689453</v>
+        <v>23241.990234</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>46022</v>
+        <v>46053</v>
       </c>
       <c r="B52" t="n">
-        <v>23241.990234</v>
+        <v>23461.820312</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B53" t="n">
-        <v>23461.820312</v>
+        <v>22668.210938</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>46081</v>
+        <v>46112</v>
       </c>
       <c r="B54" t="n">
-        <v>22668.210938</v>
+        <v>21590.630859</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>46112</v>
+        <v>46142</v>
       </c>
       <c r="B55" t="n">
-        <v>21590.630859</v>
+        <v>24892.310547</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>46142</v>
+        <v>46173</v>
       </c>
       <c r="B56" t="n">
-        <v>24892.310547</v>
+        <v>26972.619141</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="B57" t="n">
-        <v>26972.619141</v>
+        <v>26213.720703</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="B58" t="n">
-        <v>26213.720703</v>
+        <v>25373.849609</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="B59" t="n">
-        <v>25373.849609</v>
+        <v>26370.890625</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="B60" t="n">
-        <v>26370.890625</v>
+        <v>26861.060547</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="B61" t="n">
-        <v>26861.060547</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="1" t="n">
-        <v>46326</v>
-      </c>
-      <c r="B62" t="n">
-        <v>26453.009766</v>
+        <v>25479.597656</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_nasdaq.xlsx
+++ b/data/final/series/yahoo_nasdaq.xlsx
@@ -909,7 +909,7 @@
         <v>46326</v>
       </c>
       <c r="B61" t="n">
-        <v>25479.597656</v>
+        <v>25437</v>
       </c>
     </row>
   </sheetData>
